--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:48</t>
+    <t xml:space="preserve">2026-09-09 22:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:36</t>
+    <t xml:space="preserve">2026-09-12 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
@@ -39,30 +39,30 @@
     <t xml:space="preserve">Río Ibáñez</t>
   </si>
   <si>
+    <t xml:space="preserve">O'Higgins</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cisnes</t>
   </si>
   <si>
     <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
-    <t xml:space="preserve">O'Higgins</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chile Chico</t>
   </si>
   <si>
+    <t xml:space="preserve">Coyhaique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guaitecas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tortel</t>
   </si>
   <si>
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guaitecas</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:52</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>27.4</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="3">
@@ -519,13 +519,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>11202</v>
+        <v>11302</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7.8</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="4">
@@ -536,13 +536,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11301</v>
+        <v>11202</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7.23</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="5">
@@ -553,13 +553,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11302</v>
+        <v>11301</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.45</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2.59</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="7">
@@ -584,16 +584,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11303</v>
+        <v>11201</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.65</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="8">
@@ -601,16 +601,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>11201</v>
+        <v>11101</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.88</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="9">
@@ -621,13 +621,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>11102</v>
+        <v>11203</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="10">
@@ -638,13 +638,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11101</v>
+        <v>11303</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-1.33</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="11">
@@ -655,13 +655,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>11203</v>
+        <v>11102</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-10.34</v>
+        <v>-5.32</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9.06</v>
+        <v>90.64</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.17</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.15</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.73</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.59</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.04</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.44</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.92</v>
+        <v>-9.2</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-2.86</v>
+        <v>-28.57</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-5.32</v>
+        <v>-53.18</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-10-01 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:59</t>
+    <t xml:space="preserve">2026-10-02 13:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:30</t>
+    <t xml:space="preserve">2026-10-04 08:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:18</t>
+    <t xml:space="preserve">2026-10-05 08:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
